--- a/mode_docx_gen/pmi_dzt/dtz1_modes/ДТЗ_8.xlsx
+++ b/mode_docx_gen/pmi_dzt/dtz1_modes/ДТЗ_8.xlsx
@@ -593,8 +593,8 @@
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -985,59 +985,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
+        <v>0.02</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>5</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>1</v>
+        <v>0.02</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="S2" s="2" t="n">
         <v>10</v>
@@ -1052,13 +1052,13 @@
         <v>10.5</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="Z2" s="2" t="n">
         <v>1</v>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>5</v>
@@ -1084,8 +1084,8 @@
       <c r="AG2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AH2" t="n">
-        <v>0</v>
+      <c r="AH2" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>1</v>
@@ -1094,7 +1094,7 @@
         <v>0.2</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AL2" s="2" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="AY2" s="2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1371,8 +1371,8 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1393,37 +1393,37 @@
         <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>240</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="T2" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="U2" s="2" t="n">
-        <v>0.55</v>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" s="2" t="n">
-        <v>0.55</v>
+      <c r="W2" t="n">
+        <v>0</v>
       </c>
       <c r="X2" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="Y2" s="2" t="n">
-        <v>0.55</v>
+      <c r="Y2" t="n">
+        <v>0</v>
       </c>
       <c r="Z2" s="2" t="n">
         <v>120</v>
@@ -2340,32 +2340,32 @@
       </c>
       <c r="BY2" s="2" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BZ2" s="2" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="CA2" s="2" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CB2" s="2" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="CC2" s="2" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CD2" s="2" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
